--- a/Team-Data/2013-14/3-16-2013-14.xlsx
+++ b/Team-Data/2013-14/3-16-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>-0.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE2" t="n">
         <v>18</v>
@@ -751,7 +818,7 @@
         <v>18</v>
       </c>
       <c r="AH2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI2" t="n">
         <v>18</v>
@@ -778,13 +845,13 @@
         <v>22</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR2" t="n">
         <v>28</v>
       </c>
       <c r="AS2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT2" t="n">
         <v>28</v>
@@ -793,10 +860,10 @@
         <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX2" t="n">
         <v>24</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-16-2013-14</t>
+          <t>2014-03-16</t>
         </is>
       </c>
     </row>
@@ -843,40 +910,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E3" t="n">
         <v>22</v>
       </c>
       <c r="F3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G3" t="n">
-        <v>0.328</v>
+        <v>0.333</v>
       </c>
       <c r="H3" t="n">
         <v>48.1</v>
       </c>
       <c r="I3" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J3" t="n">
-        <v>84.09999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K3" t="n">
         <v>0.432</v>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M3" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.325</v>
+        <v>0.323</v>
       </c>
       <c r="O3" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="P3" t="n">
         <v>21.2</v>
@@ -888,13 +955,13 @@
         <v>12</v>
       </c>
       <c r="S3" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="T3" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="U3" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="V3" t="n">
         <v>15.4</v>
@@ -903,43 +970,43 @@
         <v>7.1</v>
       </c>
       <c r="X3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AA3" t="n">
         <v>19.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>95.5</v>
+        <v>95.2</v>
       </c>
       <c r="AC3" t="n">
         <v>-4</v>
       </c>
       <c r="AD3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE3" t="n">
         <v>25</v>
       </c>
       <c r="AF3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI3" t="n">
         <v>25</v>
       </c>
       <c r="AJ3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK3" t="n">
         <v>26</v>
@@ -948,7 +1015,7 @@
         <v>24</v>
       </c>
       <c r="AM3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN3" t="n">
         <v>28</v>
@@ -960,31 +1027,31 @@
         <v>25</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR3" t="n">
         <v>7</v>
       </c>
       <c r="AS3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT3" t="n">
         <v>14</v>
       </c>
       <c r="AU3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW3" t="n">
         <v>23</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>22</v>
       </c>
       <c r="AX3" t="n">
         <v>21</v>
       </c>
       <c r="AY3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ3" t="n">
         <v>19</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-16-2013-14</t>
+          <t>2014-03-16</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-1.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE4" t="n">
         <v>15</v>
@@ -1115,7 +1182,7 @@
         <v>15</v>
       </c>
       <c r="AH4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI4" t="n">
         <v>29</v>
@@ -1148,13 +1215,13 @@
         <v>29</v>
       </c>
       <c r="AS4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT4" t="n">
         <v>29</v>
       </c>
       <c r="AU4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV4" t="n">
         <v>12</v>
@@ -1166,13 +1233,13 @@
         <v>27</v>
       </c>
       <c r="AY4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ4" t="n">
         <v>22</v>
       </c>
       <c r="BA4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB4" t="n">
         <v>22</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-16-2013-14</t>
+          <t>2014-03-16</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E5" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F5" t="n">
         <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>0.493</v>
+        <v>0.485</v>
       </c>
       <c r="H5" t="n">
         <v>48.3</v>
@@ -1225,25 +1292,25 @@
         <v>35.9</v>
       </c>
       <c r="J5" t="n">
-        <v>81.3</v>
+        <v>81.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.442</v>
+        <v>0.44</v>
       </c>
       <c r="L5" t="n">
         <v>6</v>
       </c>
       <c r="M5" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="N5" t="n">
-        <v>0.353</v>
+        <v>0.352</v>
       </c>
       <c r="O5" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="P5" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="Q5" t="n">
         <v>0.732</v>
@@ -1261,7 +1328,7 @@
         <v>21.1</v>
       </c>
       <c r="V5" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="W5" t="n">
         <v>6.2</v>
@@ -1279,16 +1346,16 @@
         <v>21</v>
       </c>
       <c r="AB5" t="n">
-        <v>95.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.2</v>
+        <v>-1.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF5" t="n">
         <v>17</v>
@@ -1297,7 +1364,7 @@
         <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AI5" t="n">
         <v>26</v>
@@ -1315,19 +1382,19 @@
         <v>28</v>
       </c>
       <c r="AN5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AO5" t="n">
         <v>12</v>
       </c>
       <c r="AP5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ5" t="n">
         <v>24</v>
       </c>
       <c r="AR5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS5" t="n">
         <v>9</v>
@@ -1357,10 +1424,10 @@
         <v>10</v>
       </c>
       <c r="BB5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-16-2013-14</t>
+          <t>2014-03-16</t>
         </is>
       </c>
     </row>
@@ -1467,10 +1534,10 @@
         <v>1.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AE6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF6" t="n">
         <v>13</v>
@@ -1521,7 +1588,7 @@
         <v>11</v>
       </c>
       <c r="AV6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW6" t="n">
         <v>21</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-16-2013-14</t>
+          <t>2014-03-16</t>
         </is>
       </c>
     </row>
@@ -1571,40 +1638,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E7" t="n">
         <v>26</v>
       </c>
       <c r="F7" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G7" t="n">
-        <v>0.388</v>
+        <v>0.394</v>
       </c>
       <c r="H7" t="n">
         <v>48.7</v>
       </c>
       <c r="I7" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="J7" t="n">
-        <v>85.09999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0.427</v>
+        <v>0.428</v>
       </c>
       <c r="L7" t="n">
         <v>7.1</v>
       </c>
       <c r="M7" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.356</v>
+        <v>0.357</v>
       </c>
       <c r="O7" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="P7" t="n">
         <v>22.8</v>
@@ -1628,43 +1695,43 @@
         <v>14.4</v>
       </c>
       <c r="W7" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X7" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z7" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA7" t="n">
         <v>19.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>97</v>
+        <v>97.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>-4.5</v>
+        <v>-4.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG7" t="n">
         <v>22</v>
       </c>
       <c r="AH7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ7" t="n">
         <v>6</v>
@@ -1700,13 +1767,13 @@
         <v>10</v>
       </c>
       <c r="AU7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX7" t="n">
         <v>29</v>
@@ -1715,13 +1782,13 @@
         <v>27</v>
       </c>
       <c r="AZ7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA7" t="n">
         <v>22</v>
       </c>
       <c r="BB7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC7" t="n">
         <v>25</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-16-2013-14</t>
+          <t>2014-03-16</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E8" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F8" t="n">
         <v>27</v>
       </c>
       <c r="G8" t="n">
-        <v>0.597</v>
+        <v>0.591</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
@@ -1771,19 +1838,19 @@
         <v>39.4</v>
       </c>
       <c r="J8" t="n">
-        <v>83.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.473</v>
+        <v>0.472</v>
       </c>
       <c r="L8" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="M8" t="n">
         <v>22.2</v>
       </c>
       <c r="N8" t="n">
-        <v>0.383</v>
+        <v>0.38</v>
       </c>
       <c r="O8" t="n">
         <v>17</v>
@@ -1804,7 +1871,7 @@
         <v>40.2</v>
       </c>
       <c r="U8" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="V8" t="n">
         <v>13.4</v>
@@ -1819,19 +1886,19 @@
         <v>3.7</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA8" t="n">
         <v>19.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.3</v>
+        <v>104.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1843,7 +1910,7 @@
         <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
@@ -1861,7 +1928,7 @@
         <v>12</v>
       </c>
       <c r="AN8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO8" t="n">
         <v>18</v>
@@ -1897,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA8" t="n">
         <v>21</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-16-2013-14</t>
+          <t>2014-03-16</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
         <v>18</v>
@@ -2025,7 +2092,7 @@
         <v>19</v>
       </c>
       <c r="AH9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI9" t="n">
         <v>12</v>
@@ -2043,7 +2110,7 @@
         <v>9</v>
       </c>
       <c r="AN9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO9" t="n">
         <v>8</v>
@@ -2061,7 +2128,7 @@
         <v>7</v>
       </c>
       <c r="AT9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU9" t="n">
         <v>12</v>
@@ -2079,7 +2146,7 @@
         <v>24</v>
       </c>
       <c r="AZ9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BA9" t="n">
         <v>7</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-16-2013-14</t>
+          <t>2014-03-16</t>
         </is>
       </c>
     </row>
@@ -2195,13 +2262,13 @@
         <v>-3</v>
       </c>
       <c r="AD10" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
       </c>
       <c r="AF10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG10" t="n">
         <v>23</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-16-2013-14</t>
+          <t>2014-03-16</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E11" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F11" t="n">
         <v>26</v>
       </c>
       <c r="G11" t="n">
-        <v>0.618</v>
+        <v>0.612</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
@@ -2317,16 +2384,16 @@
         <v>39</v>
       </c>
       <c r="J11" t="n">
-        <v>85.09999999999999</v>
+        <v>85</v>
       </c>
       <c r="K11" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L11" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="N11" t="n">
         <v>0.377</v>
@@ -2338,40 +2405,40 @@
         <v>21.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.746</v>
+        <v>0.745</v>
       </c>
       <c r="R11" t="n">
         <v>11.1</v>
       </c>
       <c r="S11" t="n">
-        <v>34.2</v>
+        <v>34.3</v>
       </c>
       <c r="T11" t="n">
         <v>45.3</v>
       </c>
       <c r="U11" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V11" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W11" t="n">
         <v>7.9</v>
       </c>
       <c r="X11" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y11" t="n">
         <v>4.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AA11" t="n">
         <v>20</v>
       </c>
       <c r="AB11" t="n">
-        <v>103.5</v>
+        <v>103.4</v>
       </c>
       <c r="AC11" t="n">
         <v>4.6</v>
@@ -2410,7 +2477,7 @@
         <v>6</v>
       </c>
       <c r="AO11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP11" t="n">
         <v>20</v>
@@ -2428,10 +2495,10 @@
         <v>5</v>
       </c>
       <c r="AU11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AW11" t="n">
         <v>13</v>
@@ -2446,7 +2513,7 @@
         <v>21</v>
       </c>
       <c r="BA11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB11" t="n">
         <v>11</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-16-2013-14</t>
+          <t>2014-03-16</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E12" t="n">
         <v>44</v>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G12" t="n">
-        <v>0.667</v>
+        <v>0.677</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
@@ -2499,7 +2566,7 @@
         <v>37.6</v>
       </c>
       <c r="J12" t="n">
-        <v>79.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K12" t="n">
         <v>0.473</v>
@@ -2508,10 +2575,10 @@
         <v>9.1</v>
       </c>
       <c r="M12" t="n">
-        <v>25.8</v>
+        <v>25.9</v>
       </c>
       <c r="N12" t="n">
-        <v>0.352</v>
+        <v>0.351</v>
       </c>
       <c r="O12" t="n">
         <v>21.8</v>
@@ -2520,16 +2587,16 @@
         <v>31.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.699</v>
+        <v>0.698</v>
       </c>
       <c r="R12" t="n">
         <v>11.3</v>
       </c>
       <c r="S12" t="n">
-        <v>33.9</v>
+        <v>34</v>
       </c>
       <c r="T12" t="n">
-        <v>45.1</v>
+        <v>45.3</v>
       </c>
       <c r="U12" t="n">
         <v>20.7</v>
@@ -2550,19 +2617,19 @@
         <v>20.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>106.1</v>
+        <v>106.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AE12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF12" t="n">
         <v>6</v>
@@ -2571,7 +2638,7 @@
         <v>6</v>
       </c>
       <c r="AH12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI12" t="n">
         <v>17</v>
@@ -2589,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO12" t="n">
         <v>1</v>
@@ -2604,7 +2671,7 @@
         <v>15</v>
       </c>
       <c r="AS12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT12" t="n">
         <v>6</v>
@@ -2625,7 +2692,7 @@
         <v>22</v>
       </c>
       <c r="AZ12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-16-2013-14</t>
+          <t>2014-03-16</t>
         </is>
       </c>
     </row>
@@ -2741,10 +2808,10 @@
         <v>6.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF13" t="n">
         <v>2</v>
@@ -2759,7 +2826,7 @@
         <v>22</v>
       </c>
       <c r="AJ13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK13" t="n">
         <v>12</v>
@@ -2768,16 +2835,16 @@
         <v>22</v>
       </c>
       <c r="AM13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO13" t="n">
         <v>11</v>
       </c>
       <c r="AP13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ13" t="n">
         <v>5</v>
@@ -2789,16 +2856,16 @@
         <v>1</v>
       </c>
       <c r="AT13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX13" t="n">
         <v>4</v>
@@ -2816,7 +2883,7 @@
         <v>21</v>
       </c>
       <c r="BC13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-16-2013-14</t>
+          <t>2014-03-16</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F14" t="n">
         <v>20</v>
       </c>
       <c r="G14" t="n">
-        <v>0.706</v>
+        <v>0.701</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
@@ -2863,28 +2930,28 @@
         <v>39.1</v>
       </c>
       <c r="J14" t="n">
-        <v>82.2</v>
+        <v>82</v>
       </c>
       <c r="K14" t="n">
-        <v>0.476</v>
+        <v>0.477</v>
       </c>
       <c r="L14" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="N14" t="n">
-        <v>0.351</v>
+        <v>0.352</v>
       </c>
       <c r="O14" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="P14" t="n">
-        <v>29.1</v>
+        <v>29.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.727</v>
+        <v>0.728</v>
       </c>
       <c r="R14" t="n">
         <v>10.4</v>
@@ -2896,37 +2963,37 @@
         <v>43</v>
       </c>
       <c r="U14" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="V14" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W14" t="n">
         <v>8.5</v>
       </c>
       <c r="X14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y14" t="n">
         <v>3.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.6</v>
+        <v>107.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD14" t="n">
         <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF14" t="n">
         <v>5</v>
@@ -2938,7 +3005,7 @@
         <v>23</v>
       </c>
       <c r="AI14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ14" t="n">
         <v>20</v>
@@ -2953,7 +3020,7 @@
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO14" t="n">
         <v>3</v>
@@ -2977,7 +3044,7 @@
         <v>3</v>
       </c>
       <c r="AV14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW14" t="n">
         <v>7</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-16-2013-14</t>
+          <t>2014-03-16</t>
         </is>
       </c>
     </row>
@@ -3105,19 +3172,19 @@
         <v>-6.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
       </c>
       <c r="AF15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG15" t="n">
         <v>25</v>
       </c>
       <c r="AH15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI15" t="n">
         <v>16</v>
@@ -3135,7 +3202,7 @@
         <v>6</v>
       </c>
       <c r="AN15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO15" t="n">
         <v>19</v>
@@ -3147,7 +3214,7 @@
         <v>20</v>
       </c>
       <c r="AR15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS15" t="n">
         <v>13</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-16-2013-14</t>
+          <t>2014-03-16</t>
         </is>
       </c>
     </row>
@@ -3287,16 +3354,16 @@
         <v>1.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AE16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF16" t="n">
         <v>9</v>
       </c>
       <c r="AG16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH16" t="n">
         <v>16</v>
@@ -3326,7 +3393,7 @@
         <v>28</v>
       </c>
       <c r="AQ16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR16" t="n">
         <v>14</v>
@@ -3338,7 +3405,7 @@
         <v>20</v>
       </c>
       <c r="AU16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV16" t="n">
         <v>5</v>
@@ -3359,7 +3426,7 @@
         <v>29</v>
       </c>
       <c r="BB16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC16" t="n">
         <v>13</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-16-2013-14</t>
+          <t>2014-03-16</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E17" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F17" t="n">
         <v>19</v>
       </c>
       <c r="G17" t="n">
-        <v>0.703</v>
+        <v>0.698</v>
       </c>
       <c r="H17" t="n">
         <v>48.5</v>
@@ -3412,7 +3479,7 @@
         <v>76.90000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.508</v>
+        <v>0.507</v>
       </c>
       <c r="L17" t="n">
         <v>8.1</v>
@@ -3424,22 +3491,22 @@
         <v>0.37</v>
       </c>
       <c r="O17" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="P17" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.764</v>
+        <v>0.762</v>
       </c>
       <c r="R17" t="n">
         <v>7.4</v>
       </c>
       <c r="S17" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="T17" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="U17" t="n">
         <v>23.1</v>
@@ -3463,13 +3530,13 @@
         <v>20.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>104.1</v>
+        <v>103.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
@@ -3505,7 +3572,7 @@
         <v>14</v>
       </c>
       <c r="AP17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ17" t="n">
         <v>14</v>
@@ -3535,7 +3602,7 @@
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA17" t="n">
         <v>15</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-16-2013-14</t>
+          <t>2014-03-16</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E18" t="n">
         <v>13</v>
       </c>
       <c r="F18" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G18" t="n">
-        <v>0.194</v>
+        <v>0.197</v>
       </c>
       <c r="H18" t="n">
         <v>48.5</v>
@@ -3591,7 +3658,7 @@
         <v>35.6</v>
       </c>
       <c r="J18" t="n">
-        <v>82.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K18" t="n">
         <v>0.431</v>
@@ -3600,28 +3667,28 @@
         <v>7.1</v>
       </c>
       <c r="M18" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="N18" t="n">
         <v>0.354</v>
       </c>
       <c r="O18" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="P18" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.756</v>
+        <v>0.757</v>
       </c>
       <c r="R18" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="S18" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="T18" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="U18" t="n">
         <v>21.3</v>
@@ -3633,25 +3700,25 @@
         <v>6.7</v>
       </c>
       <c r="X18" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>94.5</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC18" t="n">
         <v>-8.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3663,7 +3730,7 @@
         <v>30</v>
       </c>
       <c r="AH18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI18" t="n">
         <v>28</v>
@@ -3690,13 +3757,13 @@
         <v>23</v>
       </c>
       <c r="AQ18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT18" t="n">
         <v>25</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-16-2013-14</t>
+          <t>2014-03-16</t>
         </is>
       </c>
     </row>
@@ -3755,25 +3822,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E19" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F19" t="n">
         <v>32</v>
       </c>
       <c r="G19" t="n">
-        <v>0.508</v>
+        <v>0.5</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="J19" t="n">
-        <v>87.59999999999999</v>
+        <v>87.7</v>
       </c>
       <c r="K19" t="n">
         <v>0.44</v>
@@ -3782,28 +3849,28 @@
         <v>7.4</v>
       </c>
       <c r="M19" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="N19" t="n">
         <v>0.341</v>
       </c>
       <c r="O19" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="P19" t="n">
-        <v>27.9</v>
+        <v>27.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.778</v>
+        <v>0.777</v>
       </c>
       <c r="R19" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="S19" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="T19" t="n">
-        <v>45.1</v>
+        <v>45.3</v>
       </c>
       <c r="U19" t="n">
         <v>23.3</v>
@@ -3818,7 +3885,7 @@
         <v>3.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z19" t="n">
         <v>18.5</v>
@@ -3830,13 +3897,13 @@
         <v>106.1</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AD19" t="n">
         <v>26</v>
       </c>
       <c r="AE19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF19" t="n">
         <v>16</v>
@@ -3848,7 +3915,7 @@
         <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ19" t="n">
         <v>2</v>
@@ -3860,7 +3927,7 @@
         <v>17</v>
       </c>
       <c r="AM19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN19" t="n">
         <v>26</v>
@@ -3872,10 +3939,10 @@
         <v>3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS19" t="n">
         <v>12</v>
@@ -3905,7 +3972,7 @@
         <v>3</v>
       </c>
       <c r="BB19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC19" t="n">
         <v>9</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-16-2013-14</t>
+          <t>2014-03-16</t>
         </is>
       </c>
     </row>
@@ -3937,100 +4004,100 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F20" t="n">
         <v>39</v>
       </c>
       <c r="G20" t="n">
-        <v>0.409</v>
+        <v>0.4</v>
       </c>
       <c r="H20" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I20" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="J20" t="n">
-        <v>83.2</v>
+        <v>83</v>
       </c>
       <c r="K20" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L20" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="M20" t="n">
         <v>16</v>
       </c>
       <c r="N20" t="n">
-        <v>0.372</v>
+        <v>0.375</v>
       </c>
       <c r="O20" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="P20" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.772</v>
+        <v>0.77</v>
       </c>
       <c r="R20" t="n">
         <v>11.8</v>
       </c>
       <c r="S20" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="T20" t="n">
         <v>42.1</v>
       </c>
       <c r="U20" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="V20" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W20" t="n">
         <v>8</v>
       </c>
       <c r="X20" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.8</v>
+        <v>99.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>-2.5</v>
+        <v>-2.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AE20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF20" t="n">
         <v>20</v>
       </c>
       <c r="AG20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AI20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ20" t="n">
         <v>15</v>
@@ -4054,10 +4121,10 @@
         <v>17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS20" t="n">
         <v>25</v>
@@ -4069,7 +4136,7 @@
         <v>18</v>
       </c>
       <c r="AV20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW20" t="n">
         <v>12</v>
@@ -4081,10 +4148,10 @@
         <v>28</v>
       </c>
       <c r="AZ20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB20" t="n">
         <v>18</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-16-2013-14</t>
+          <t>2014-03-16</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-1.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE21" t="n">
         <v>20</v>
@@ -4206,10 +4273,10 @@
         <v>21</v>
       </c>
       <c r="AG21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI21" t="n">
         <v>19</v>
@@ -4227,7 +4294,7 @@
         <v>5</v>
       </c>
       <c r="AN21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO21" t="n">
         <v>30</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-16-2013-14</t>
+          <t>2014-03-16</t>
         </is>
       </c>
     </row>
@@ -4301,37 +4368,37 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E22" t="n">
         <v>48</v>
       </c>
       <c r="F22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G22" t="n">
-        <v>0.727</v>
+        <v>0.738</v>
       </c>
       <c r="H22" t="n">
         <v>48.2</v>
       </c>
       <c r="I22" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="J22" t="n">
-        <v>82.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.474</v>
+        <v>0.475</v>
       </c>
       <c r="L22" t="n">
         <v>7.8</v>
       </c>
       <c r="M22" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="N22" t="n">
-        <v>0.36</v>
+        <v>0.361</v>
       </c>
       <c r="O22" t="n">
         <v>19.9</v>
@@ -4340,19 +4407,19 @@
         <v>24.7</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.804</v>
+        <v>0.806</v>
       </c>
       <c r="R22" t="n">
         <v>11.1</v>
       </c>
       <c r="S22" t="n">
-        <v>34.2</v>
+        <v>34.4</v>
       </c>
       <c r="T22" t="n">
-        <v>45.3</v>
+        <v>45.5</v>
       </c>
       <c r="U22" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="V22" t="n">
         <v>15.8</v>
@@ -4361,31 +4428,31 @@
         <v>8.300000000000001</v>
       </c>
       <c r="X22" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Y22" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Z22" t="n">
         <v>22.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>105.8</v>
+        <v>106.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
       </c>
       <c r="AF22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
         <v>3</v>
@@ -4394,7 +4461,7 @@
         <v>25</v>
       </c>
       <c r="AI22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ22" t="n">
         <v>18</v>
@@ -4406,10 +4473,10 @@
         <v>16</v>
       </c>
       <c r="AM22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO22" t="n">
         <v>5</v>
@@ -4427,10 +4494,10 @@
         <v>2</v>
       </c>
       <c r="AT22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AU22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV22" t="n">
         <v>27</v>
@@ -4451,10 +4518,10 @@
         <v>18</v>
       </c>
       <c r="BB22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-16-2013-14</t>
+          <t>2014-03-16</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-5.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>28</v>
@@ -4582,13 +4649,13 @@
         <v>12</v>
       </c>
       <c r="AK23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL23" t="n">
         <v>20</v>
       </c>
       <c r="AM23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN23" t="n">
         <v>24</v>
@@ -4615,7 +4682,7 @@
         <v>20</v>
       </c>
       <c r="AV23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW23" t="n">
         <v>14</v>
@@ -4627,13 +4694,13 @@
         <v>25</v>
       </c>
       <c r="AZ23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
       </c>
       <c r="BB23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC23" t="n">
         <v>26</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-16-2013-14</t>
+          <t>2014-03-16</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-11.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4755,10 +4822,10 @@
         <v>29</v>
       </c>
       <c r="AH24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ24" t="n">
         <v>1</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-16-2013-14</t>
+          <t>2014-03-16</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E25" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F25" t="n">
         <v>28</v>
       </c>
       <c r="G25" t="n">
-        <v>0.576</v>
+        <v>0.569</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
@@ -4865,7 +4932,7 @@
         <v>38.6</v>
       </c>
       <c r="J25" t="n">
-        <v>83.90000000000001</v>
+        <v>84</v>
       </c>
       <c r="K25" t="n">
         <v>0.46</v>
@@ -4877,22 +4944,22 @@
         <v>25.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.372</v>
+        <v>0.371</v>
       </c>
       <c r="O25" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="P25" t="n">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.759</v>
+        <v>0.756</v>
       </c>
       <c r="R25" t="n">
         <v>11.6</v>
       </c>
       <c r="S25" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T25" t="n">
         <v>43.2</v>
@@ -4901,10 +4968,10 @@
         <v>19.3</v>
       </c>
       <c r="V25" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="W25" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X25" t="n">
         <v>4.7</v>
@@ -4913,28 +4980,28 @@
         <v>4.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>105.4</v>
+        <v>105.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AE25" t="n">
         <v>11</v>
       </c>
       <c r="AF25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH25" t="n">
         <v>21</v>
@@ -4943,7 +5010,7 @@
         <v>9</v>
       </c>
       <c r="AJ25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK25" t="n">
         <v>8</v>
@@ -4955,19 +5022,19 @@
         <v>3</v>
       </c>
       <c r="AN25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO25" t="n">
         <v>9</v>
       </c>
-      <c r="AO25" t="n">
-        <v>8</v>
-      </c>
       <c r="AP25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AQ25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS25" t="n">
         <v>16</v>
@@ -4979,7 +5046,7 @@
         <v>29</v>
       </c>
       <c r="AV25" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AW25" t="n">
         <v>9</v>
@@ -4988,7 +5055,7 @@
         <v>17</v>
       </c>
       <c r="AY25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ25" t="n">
         <v>23</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-16-2013-14</t>
+          <t>2014-03-16</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E26" t="n">
         <v>43</v>
       </c>
       <c r="F26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G26" t="n">
-        <v>0.642</v>
+        <v>0.652</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
@@ -5050,7 +5117,7 @@
         <v>87.5</v>
       </c>
       <c r="K26" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L26" t="n">
         <v>9.4</v>
@@ -5059,16 +5126,16 @@
         <v>25</v>
       </c>
       <c r="N26" t="n">
-        <v>0.376</v>
+        <v>0.375</v>
       </c>
       <c r="O26" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="P26" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.819</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="R26" t="n">
         <v>12.7</v>
@@ -5095,19 +5162,19 @@
         <v>3.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>107.4</v>
+        <v>107.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
@@ -5149,7 +5216,7 @@
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS26" t="n">
         <v>6</v>
@@ -5158,7 +5225,7 @@
         <v>1</v>
       </c>
       <c r="AU26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV26" t="n">
         <v>6</v>
@@ -5170,13 +5237,13 @@
         <v>13</v>
       </c>
       <c r="AY26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ26" t="n">
         <v>7</v>
       </c>
       <c r="BA26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB26" t="n">
         <v>2</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-16-2013-14</t>
+          <t>2014-03-16</t>
         </is>
       </c>
     </row>
@@ -5211,28 +5278,28 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E27" t="n">
         <v>23</v>
       </c>
       <c r="F27" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G27" t="n">
-        <v>0.343</v>
+        <v>0.348</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
       </c>
       <c r="I27" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J27" t="n">
         <v>82.59999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L27" t="n">
         <v>6.3</v>
@@ -5244,10 +5311,10 @@
         <v>0.335</v>
       </c>
       <c r="O27" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="P27" t="n">
-        <v>27.3</v>
+        <v>27.4</v>
       </c>
       <c r="Q27" t="n">
         <v>0.766</v>
@@ -5277,10 +5344,10 @@
         <v>5.6</v>
       </c>
       <c r="Z27" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="AB27" t="n">
         <v>101.1</v>
@@ -5289,7 +5356,7 @@
         <v>-2.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
@@ -5343,7 +5410,7 @@
         <v>30</v>
       </c>
       <c r="AV27" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AW27" t="n">
         <v>19</v>
@@ -5355,7 +5422,7 @@
         <v>23</v>
       </c>
       <c r="AZ27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA27" t="n">
         <v>4</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-16-2013-14</t>
+          <t>2014-03-16</t>
         </is>
       </c>
     </row>
@@ -5393,28 +5460,28 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E28" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F28" t="n">
         <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>0.758</v>
+        <v>0.754</v>
       </c>
       <c r="H28" t="n">
         <v>48.2</v>
       </c>
       <c r="I28" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="J28" t="n">
         <v>82.5</v>
       </c>
       <c r="K28" t="n">
-        <v>0.49</v>
+        <v>0.488</v>
       </c>
       <c r="L28" t="n">
         <v>8.300000000000001</v>
@@ -5423,34 +5490,34 @@
         <v>20.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0.4</v>
+        <v>0.398</v>
       </c>
       <c r="O28" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="P28" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="Q28" t="n">
         <v>0.787</v>
       </c>
       <c r="R28" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="S28" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="T28" t="n">
         <v>42.9</v>
       </c>
       <c r="U28" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="V28" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W28" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X28" t="n">
         <v>5.1</v>
@@ -5465,13 +5532,13 @@
         <v>19.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>105.1</v>
+        <v>104.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5498,7 +5565,7 @@
         <v>11</v>
       </c>
       <c r="AM28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN28" t="n">
         <v>1</v>
@@ -5516,10 +5583,10 @@
         <v>27</v>
       </c>
       <c r="AS28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU28" t="n">
         <v>2</v>
@@ -5528,7 +5595,7 @@
         <v>15</v>
       </c>
       <c r="AW28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX28" t="n">
         <v>11</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-16-2013-14</t>
+          <t>2014-03-16</t>
         </is>
       </c>
     </row>
@@ -5575,28 +5642,28 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E29" t="n">
         <v>37</v>
       </c>
       <c r="F29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G29" t="n">
-        <v>0.569</v>
+        <v>0.578</v>
       </c>
       <c r="H29" t="n">
         <v>48.6</v>
       </c>
       <c r="I29" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J29" t="n">
         <v>82</v>
       </c>
       <c r="K29" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L29" t="n">
         <v>8.4</v>
@@ -5605,7 +5672,7 @@
         <v>22.8</v>
       </c>
       <c r="N29" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="O29" t="n">
         <v>19.2</v>
@@ -5614,25 +5681,25 @@
         <v>24.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.778</v>
+        <v>0.777</v>
       </c>
       <c r="R29" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S29" t="n">
-        <v>31.2</v>
+        <v>31.4</v>
       </c>
       <c r="T29" t="n">
-        <v>42.7</v>
+        <v>43</v>
       </c>
       <c r="U29" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V29" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W29" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X29" t="n">
         <v>4.3</v>
@@ -5641,40 +5708,40 @@
         <v>4.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AA29" t="n">
         <v>22</v>
       </c>
       <c r="AB29" t="n">
-        <v>100.5</v>
+        <v>100.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD29" t="n">
         <v>26</v>
       </c>
       <c r="AE29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG29" t="n">
         <v>11</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>12</v>
       </c>
       <c r="AH29" t="n">
         <v>5</v>
       </c>
       <c r="AI29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL29" t="n">
         <v>9</v>
@@ -5689,19 +5756,19 @@
         <v>7</v>
       </c>
       <c r="AP29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AQ29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AR29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS29" t="n">
         <v>19</v>
       </c>
       <c r="AT29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU29" t="n">
         <v>16</v>
@@ -5710,7 +5777,7 @@
         <v>9</v>
       </c>
       <c r="AW29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX29" t="n">
         <v>22</v>
@@ -5719,7 +5786,7 @@
         <v>11</v>
       </c>
       <c r="AZ29" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BA29" t="n">
         <v>5</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-16-2013-14</t>
+          <t>2014-03-16</t>
         </is>
       </c>
     </row>
@@ -5757,25 +5824,25 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E30" t="n">
         <v>22</v>
       </c>
       <c r="F30" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G30" t="n">
-        <v>0.328</v>
+        <v>0.333</v>
       </c>
       <c r="H30" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="I30" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J30" t="n">
-        <v>81</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K30" t="n">
         <v>0.443</v>
@@ -5784,10 +5851,10 @@
         <v>6.8</v>
       </c>
       <c r="M30" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="N30" t="n">
-        <v>0.354</v>
+        <v>0.353</v>
       </c>
       <c r="O30" t="n">
         <v>16.3</v>
@@ -5799,10 +5866,10 @@
         <v>0.748</v>
       </c>
       <c r="R30" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S30" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="T30" t="n">
         <v>41.5</v>
@@ -5811,7 +5878,7 @@
         <v>20</v>
       </c>
       <c r="V30" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W30" t="n">
         <v>6.8</v>
@@ -5823,37 +5890,37 @@
         <v>4.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA30" t="n">
         <v>20.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>94.90000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>-6.2</v>
+        <v>-6</v>
       </c>
       <c r="AD30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
         <v>25</v>
       </c>
       <c r="AF30" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH30" t="n">
         <v>26</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AI30" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ30" t="n">
         <v>26</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>26</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>25</v>
       </c>
       <c r="AK30" t="n">
         <v>23</v>
@@ -5862,19 +5929,19 @@
         <v>21</v>
       </c>
       <c r="AM30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN30" t="n">
         <v>19</v>
       </c>
       <c r="AO30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP30" t="n">
         <v>21</v>
       </c>
       <c r="AQ30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR30" t="n">
         <v>20</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-16-2013-14</t>
+          <t>2014-03-16</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>0.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6032,7 +6099,7 @@
         <v>1</v>
       </c>
       <c r="AI31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ31" t="n">
         <v>8</v>
@@ -6044,7 +6111,7 @@
         <v>15</v>
       </c>
       <c r="AM31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN31" t="n">
         <v>2</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-16-2013-14</t>
+          <t>2014-03-16</t>
         </is>
       </c>
     </row>
